--- a/DesignData/Excel_Masters/CharacterAwakenData_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAwakenData_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17910" windowHeight="10695"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15420" windowHeight="10965"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterAwakenData" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>RequiredSoulstone</t>
-  </si>
-  <si>
     <t>RequiredGold</t>
   </si>
   <si>
@@ -34,6 +31,9 @@
   </si>
   <si>
     <t>BonusStatMultiplier</t>
+  </si>
+  <si>
+    <t>RequiredAwakeningPieces</t>
   </si>
 </sst>
 </file>
@@ -959,16 +959,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">

--- a/DesignData/Excel_Masters/CharacterAwakenData_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAwakenData_Master.xlsx
@@ -951,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -973,24 +973,24 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>1.0249999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -999,15 +999,15 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>1.05</v>
+        <v>1.0249999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1016,15 +1016,15 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>1.085</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1033,15 +1033,15 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E5">
-        <v>1.125</v>
+        <v>1.085</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1050,15 +1050,15 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E6">
-        <v>1.1499999999999999</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1067,14 +1067,32 @@
         <v>0</v>
       </c>
       <c r="D7">
+        <v>55</v>
+      </c>
+      <c r="E7">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>60</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>1.2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>